--- a/_setup/BOTB-2027-신청자-도표.xlsx
+++ b/_setup/BOTB-2027-신청자-도표.xlsx
@@ -512,27 +512,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
-    <col width="40" customWidth="1" min="18" max="18"/>
+    <col width="42" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -567,75 +566,70 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>부문</t>
+          <t>선수1 이름</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>선수1 이름</t>
+          <t>영문명</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>나이</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>연락처</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>이메일</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>핸디</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>선수2 이름</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>영문명</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>나이</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>연락처</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>이메일</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>핸디</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>선수2 이름</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>영문명</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>나이</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>연락처</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>이메일</t>
-        </is>
-      </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>핸디</t>
+          <t>스폰서</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>스폰서</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -657,67 +651,62 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>혼성부</t>
+          <t>크리스 변</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>크리스 변</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
           <t>KRIS BYUN</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>516-776-0110</t>
+        </is>
+      </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>516-776-0110</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
           <t>kris0193@gmail.com</t>
         </is>
       </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>11–15</t>
+        </is>
+      </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
+          <t>미쉘 최</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>MICHELLE CHOI</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>917-232-7565</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>c.miok@yahoo.com</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
           <t>11–15</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>미쉘 최</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>MICHELLE CHOI</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="5" t="inlineStr">
-        <is>
-          <t>917-232-7565</t>
-        </is>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>c.miok@yahoo.com</t>
-        </is>
-      </c>
       <c r="P5" s="4" t="inlineStr">
         <is>
-          <t>11–15</t>
-        </is>
-      </c>
-      <c r="Q5" s="4" t="inlineStr">
-        <is>
           <t>아니오</t>
         </is>
       </c>
-      <c r="R5" s="5" t="inlineStr">
+      <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>소속 지역 '기타' — 516/917 뉴욕 번호. NY 팀으로 넣을지 확인</t>
         </is>
@@ -739,67 +728,62 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>혼성부</t>
+          <t>안 성수</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>안 성수</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
           <t>AHN SUNGSU</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>201-995-7800</t>
+        </is>
+      </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>201-995-7800</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
           <t>ssa2021nj@gmail.com</t>
         </is>
       </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>16–20</t>
+        </is>
+      </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
+          <t>김 경임</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>KIM KYUNG IM</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr"/>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>205-534-9112</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>kyungimk@gmail.com</t>
+        </is>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
           <t>16–20</t>
         </is>
       </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>김 경임</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>KIM KYUNG IM</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>205-534-9112</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>kyungimk@gmail.com</t>
-        </is>
-      </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>16–20</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
           <t>아니오</t>
         </is>
       </c>
-      <c r="R6" s="7" t="inlineStr">
+      <c r="Q6" s="7" t="inlineStr">
         <is>
           <t>소속 지역 '기타' — 선수1 NJ(201) / 선수2 AL(205). 팀 소속 확정 필요</t>
         </is>
@@ -821,69 +805,64 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>남성부</t>
+          <t>박승원</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>박승원</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
           <t>Sung won Park</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>470-965-8736</t>
+        </is>
+      </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>470-965-8736</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
           <t>jaemo8381@gmail.com</t>
         </is>
       </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>6–10</t>
+        </is>
+      </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
+          <t>모재완</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>Jae Mo</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>678-787-4069</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>jaemo8381@gmail.com</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
           <t>6–10</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>모재완</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>Jae Mo</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr"/>
-      <c r="N7" s="5" t="inlineStr">
-        <is>
-          <t>678-787-4069</t>
-        </is>
-      </c>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>jaemo8381@gmail.com</t>
-        </is>
-      </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>6–10</t>
-        </is>
-      </c>
-      <c r="Q7" s="4" t="inlineStr">
-        <is>
           <t>아니오</t>
         </is>
       </c>
-      <c r="R7" s="5" t="inlineStr">
-        <is>
-          <t>두 선수 모두 모재완 이메일로 접수. 박승원 개인 메일은 Parkwireless1@gmail.com 로 보임 — 확인 필요</t>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>두 선수 모두 모재완 이메일(jaemo8381@gmail.com)로 접수 — 박승원 개인 이메일 확인 필요</t>
         </is>
       </c>
     </row>
@@ -903,75 +882,70 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>시니어부</t>
+          <t>데이빗조</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>데이빗조</t>
+          <t>David Jo</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>David Jo</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
           <t>59</t>
         </is>
       </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>334-544-9200</t>
+        </is>
+      </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>334-544-9200</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
           <t>whitestone9867@yahoo.com</t>
         </is>
       </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>6–10</t>
+        </is>
+      </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
+          <t>허춘배</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>Chun Bae Hur</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>334-444-8688</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>hurbae@gmai.com</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
           <t>6–10</t>
         </is>
       </c>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>허춘배</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>Chun Bae Hur</t>
-        </is>
-      </c>
-      <c r="M8" s="6" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>334-444-8688</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>hurbae@gmai.com</t>
-        </is>
-      </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>6–10</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
           <t>아니오</t>
         </is>
       </c>
-      <c r="R8" s="7" t="inlineStr">
+      <c r="Q8" s="7" t="inlineStr">
         <is>
           <t>선수2 이메일 오타 의심 (gmai.com → gmail.com)</t>
         </is>
@@ -993,112 +967,183 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>여성부</t>
+          <t>강은영</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>강은영</t>
+          <t>Key Kang</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Key Kang</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
           <t>53</t>
         </is>
       </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>646-734-3999</t>
+        </is>
+      </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>646-734-3999</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
           <t>keylpga@gmail.com</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr"/>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>박민희</t>
+        </is>
+      </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>박민희</t>
+          <t>Min Park</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>Min Park</t>
-        </is>
-      </c>
-      <c r="M9" s="4" t="inlineStr">
-        <is>
           <t>55</t>
         </is>
       </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>917-885-9162</t>
+        </is>
+      </c>
       <c r="N9" s="5" t="inlineStr">
         <is>
-          <t>917-885-9162</t>
-        </is>
-      </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
           <t>yura3lee@yahoo.com</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr"/>
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>아니오</t>
         </is>
       </c>
-      <c r="R9" s="5" t="inlineStr">
+      <c r="Q9" s="5" t="inlineStr">
         <is>
           <t>두 선수 모두 핸디캡 미기재</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>FL · 플로리다</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>오명섭</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>813-560-4367</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>goodohwithus@gmail.com</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>스크래치~5</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>박용호</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr"/>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>813-857-8143</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>parkwireless1@gmail.com</t>
+        </is>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>6–10</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>아니오</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>대회 운영진 (경기위원장 · 대회 준비위원장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>5팀 · 10명</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" s="8" t="inlineStr">
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>6팀 · 12명</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" s="8" t="inlineStr">
         <is>
           <t>잔여</t>
         </is>
       </c>
-      <c r="R11" s="8" t="inlineStr">
-        <is>
-          <t>19팀</t>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>18팀</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1110,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1201,193 +1246,140 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>■ 부문별</t>
-        </is>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>FL · 플로리다</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>■ 핸디캡별 (인원)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>팀 수</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>인원</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>혼성부</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>남성부</t>
+          <t>6–10</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>시니어부</t>
+          <t>11–15</t>
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="12" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>여성부</t>
+          <t>16–20</t>
         </is>
       </c>
       <c r="B16" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>미기재</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>스크래치~5</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="12" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>■ 핸디캡별 (인원)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>인원</t>
-        </is>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>6–10</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="n">
-        <v>4</v>
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>■ 정원 현황</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>11–15</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="n">
-        <v>2</v>
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>정원</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>24팀 (48명)</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>16–20</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="n">
-        <v>2</v>
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>접수</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>6팀 (12명)</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>미기재</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>■ 정원 현황</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>정원</t>
-        </is>
-      </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>24팀 (48명)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>접수</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>5팀 (10명)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>잔여</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>19팀 (38명)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>18팀 (36명)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>접수율</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>21%</t>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>25%</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1480,7 +1472,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>박승원 개인 메일 Parkwireless1@gmail.com 확인</t>
+          <t>박승원 개인 이메일 확인</t>
         </is>
       </c>
     </row>
@@ -1509,108 +1501,130 @@
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>안 성수 · 김 경임</t>
+          <t>기존 접수 6팀 전체</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>소속 지역 '기타 지역' — 선수1 NJ(201) / 선수2 AL(205)</t>
+          <t>신청 당시 선택했던 부문(남성부·여성부·혼성부·시니어부)은 이제 쓰지 않음</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>팀 소속 지역 확정</t>
+          <t>시트의 부문 열은 기록용으로만 보관</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>강은영 · 박민희 (NJ)</t>
+          <t>안 성수 · 김 경임</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>두 선수 모두 핸디캡 미기재</t>
+          <t>소속 지역 '기타 지역' — 선수1 NJ(201) / 선수2 AL(205)</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>핸디 확인 후 입력</t>
+          <t>팀 소속 지역 확정</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026. 8. 23 이전 접수 3팀</t>
+          <t>강은영 · 박민희 (NJ)</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>나이 미기재 — 당시 신청서에 나이 칸이 없었음</t>
+          <t>두 선수 모두 핸디캡 미기재 — 부문이 없어 대진이 핸디로만 갈림</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>연락해서 나이 확보 (시니어부 판정에 필요)</t>
+          <t>반드시 핸디 확인</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>NY 남성부 2건 (9/3, 9/15)</t>
+          <t>2026. 8. 25 이전 접수 3팀</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>무작위 문자 이름 · 점 찍기 임시 이메일 — 봇 자동등록</t>
+          <t>나이 미기재 — 당시 신청서에 나이 칸이 없었음</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>구글 시트에서 행 삭제</t>
+          <t>연락해서 나이 확보 (시니어부 판정에 필요)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>NY 남성부 2건 (9/3, 9/15)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>무작위 문자 이름 · 점 찍기 임시 이메일 — 봇 자동등록</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>구글 시트에서 행 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>2026. 8. 27 접수 1건</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>모든 칸이 빈 줄 — 설치 확인용 테스트</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>구글 시트에서 행 삭제</t>
         </is>
